--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-10).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-10).xlsx
@@ -912,21 +912,21 @@
   </si>
   <si>
     <t>214
-178</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>R$ 829.620,22</t>
-  </si>
-  <si>
-    <t>R$ 4.389,52
-R$ 4.452,50</t>
-  </si>
-  <si>
-    <t>(5.7%)
-(4.4%)</t>
+183</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>R$ 851.982,39</t>
+  </si>
+  <si>
+    <t>R$ 4.391,66
+R$ 4.453,05</t>
+  </si>
+  <si>
+    <t>(5.8%)
+(5.0%)</t>
   </si>
   <si>
     <t>48.3</t>
@@ -935,10 +935,10 @@
     <t>(12.9%)</t>
   </si>
   <si>
-    <t>42.0%</t>
-  </si>
-  <si>
-    <t>(1.7%)</t>
+    <t>21.1%</t>
+  </si>
+  <si>
+    <t>(22.4%)</t>
   </si>
   <si>
     <t>4.0%</t>
@@ -947,34 +947,34 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>27.6</t>
-  </si>
-  <si>
-    <t>67.0%</t>
-  </si>
-  <si>
-    <t>11.8%</t>
+    <t>27.5</t>
+  </si>
+  <si>
+    <t>67.4%</t>
+  </si>
+  <si>
+    <t>11.6%</t>
   </si>
   <si>
     <t>5.0</t>
   </si>
   <si>
-    <t>7.5</t>
-  </si>
-  <si>
-    <t>12.6</t>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>12.5</t>
   </si>
   <si>
     <t>19.1</t>
   </si>
   <si>
-    <t>70.1%</t>
-  </si>
-  <si>
-    <t>-R$ 27.460,48</t>
-  </si>
-  <si>
-    <t>2.97</t>
+    <t>70.4%</t>
+  </si>
+  <si>
+    <t>-R$ 27.594,88</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -1411,7 +1411,7 @@
     <col min="14" max="14" width="12.14" customWidth="1"/>
     <col min="15" max="15" width="15.29" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="6.86" customWidth="1"/>
+    <col min="17" max="17" width="7.71" customWidth="1"/>
     <col min="18" max="18" width="10.14" customWidth="1"/>
     <col min="19" max="19" width="13.71" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>8222.1800000000003</v>
+      </c>
+      <c r="P6" s="5">
+        <v>8222.1800000000003</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>-0.0037018053419898278</v>
+      </c>
+      <c r="R6" s="7">
+        <v>93</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.32524075123629015</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0.0063326271134905819</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.044640971129311209</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.010379984383703593</v>
+      </c>
+      <c r="X6" s="8">
+        <v>20.557206756756759</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.91891891891891897</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>4.841392307692308</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.279054054054054</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>7.063288</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>14.020720270270271</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.98648648648648651</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -4388,7 +4424,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4424,25 +4460,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>4835.8299999999999</v>
+      </c>
+      <c r="P24" s="5">
+        <v>4835.8299999999999</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0.20835332333833079</v>
+      </c>
+      <c r="R24" s="7">
+        <v>58</v>
+      </c>
+      <c r="S24" s="6">
+        <v>0.11538461538461542</v>
+      </c>
+      <c r="T24" s="6">
+        <v>0</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.33979275532845449</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.065763374643029227</v>
+      </c>
+      <c r="W24" s="6">
+        <v>0.022223796121865327</v>
+      </c>
+      <c r="X24" s="8">
+        <v>30.265078571428571</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.61904761904761907</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>3.9628649122807018</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>7.46587380952381</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>18.52777857142857</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-134.40000000000001</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5920,7 +5990,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5956,25 +6026,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>4154.3900000000003</v>
+      </c>
+      <c r="P36" s="5">
+        <v>4154.3900000000003</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>-0.16972809848810355</v>
+      </c>
+      <c r="R36" s="7">
+        <v>31</v>
+      </c>
+      <c r="S36" s="6">
+        <v>-0.4464285714285714</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.33621530477398609</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.02161797520213557</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.074534047116423835</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.02806753819453638</v>
+      </c>
+      <c r="X36" s="8">
+        <v>32.427777777777777</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>8.2435483870967747</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>5.3712944444444446</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>15.67037</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>22.611111111111111</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.55555555555555558</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7841,7 +7947,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7877,11 +7983,21 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
+      <c r="O51" s="5">
+        <v>0</v>
+      </c>
+      <c r="P51" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R51" s="7">
+        <v>0</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-1</v>
+      </c>
       <c r="T51" s="6"/>
       <c r="U51" s="6"/>
       <c r="V51" s="6"/>
@@ -7895,7 +8011,9 @@
       <c r="AD51" s="8"/>
       <c r="AE51" s="6"/>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -11041,7 +11159,7 @@
         <v>0.023759220757027716</v>
       </c>
       <c r="W76" s="6">
-        <v>-0.0147244453305232</v>
+        <v>-0.015971917632650736</v>
       </c>
       <c r="X76" s="8">
         <v>22.597082499999999</v>
@@ -12600,7 +12718,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12639,7 +12757,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12673,25 +12791,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>2027.27</v>
+      </c>
+      <c r="P89" s="5">
+        <v>2027.27</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.68481547758787698</v>
+      </c>
+      <c r="R89" s="7">
+        <v>22</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.65079365079365081</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-85.745708021131861</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-86.115816590784647</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.056310950194103399</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0088185096213133918</v>
+      </c>
+      <c r="X89" s="8">
+        <v>30.385000000000002</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>7.7272727272727275</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>3.7277777777777774</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>21.716670000000001</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -15437,7 +15589,9 @@
       <c r="AB111" s="8">
         <v>3.1111</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>16.238887999999999</v>
+      </c>
       <c r="AD111" s="8">
         <v>23.111099999999997</v>
       </c>
@@ -15449,7 +15603,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15802,7 +15956,7 @@
         <v>-108.7</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -16677,7 +16831,7 @@
         <v>-127.7</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -16939,7 +17093,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17332,7 +17486,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18509,7 +18663,7 @@
         <v>-84.400000000000006</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -18640,7 +18794,7 @@
         <v>-205.40000000000001</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20827,7 +20981,7 @@
         <v>-2045.73</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -20954,7 +21108,7 @@
         <v>0</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -21384,7 +21538,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21420,25 +21574,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>3122.5</v>
+      </c>
+      <c r="P158" s="5">
+        <v>3122.5</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.35462735801285161</v>
+      </c>
+      <c r="R158" s="7">
+        <v>31</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.39215686274509809</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.30426920736589269</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.011340464371497199</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.026924579663730984</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.012162690152121697</v>
+      </c>
+      <c r="X158" s="8">
+        <v>25.750695833333335</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>5.4989258064516129</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>1.8868041666666666</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>7.5319430000000001</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>14.470833333333333</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.875</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22075,7 +22265,7 @@
         <v>-1191.8299999999999</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24153,7 +24343,9 @@
       <c r="AB179" s="8">
         <v>2.1106068181818181</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>4.5325749999999996</v>
+      </c>
       <c r="AD179" s="8">
         <v>11.489772727272728</v>
       </c>
@@ -28238,7 +28430,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
